--- a/example/i18n/langs/tw/equip.xlsx
+++ b/example/i18n/langs/tw/equip.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="equip.jewelrysuit" r:id="rId3" sheetId="1"/>
+    <sheet name="equip.jewelry_suit" r:id="rId3" sheetId="1"/>
   </sheets>
   <definedNames/>
 </workbook>
